--- a/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-Hauptversicherter.xlsx
+++ b/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-Hauptversicherter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="274">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:59:22+00:00</t>
+    <t>2024-11-06T11:18:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,13 +102,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Person</t>
+    <t>RelatedPerson</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Person</t>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: Interface Pattern</t>
   </si>
   <si>
     <t>Mapping: HL7 V2 Mapping</t>
@@ -250,26 +253,26 @@
 </t>
   </si>
   <si>
-    <t>A generic person record</t>
-  </si>
-  <si>
-    <t>Demographics and administrative information about a person independent of a specific health-related context.</t>
-  </si>
-  <si>
-    <t>The Person resource does justice to person registries that keep track of persons regardless of their role. The Person resource is also a primary resource to point to for people acting in a particular role such as SubjectofCare, Practitioner, and Agent. Very few attributes are specific to any role and so Person is kept lean. Most attributes are expected to be tied to the role the Person plays rather than the Person himself. Examples of that are Guardian (SubjectofCare), ContactParty (SubjectOfCare, Practitioner), and multipleBirthInd (SubjectofCare).</t>
+    <t>A person that is related to a patient, but who is not a direct target of care</t>
+  </si>
+  <si>
+    <t>Information about a person that is involved in a patient's health or the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
-    <t>administrative.entity</t>
-  </si>
-  <si>
-    <t>Entity, Role, or Act,Person(classCode="PSN" and determinerCode="INST" and quantity="1")</t>
-  </si>
-  <si>
-    <t>Person.id</t>
+    <t>administrative.individual</t>
+  </si>
+  <si>
+    <t>Entity, Role, or Act,role</t>
+  </si>
+  <si>
+    <t>ParticipantLiving</t>
+  </si>
+  <si>
+    <t>RelatedPerson.id</t>
   </si>
   <si>
     <t>1</t>
@@ -294,7 +297,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>Person.meta</t>
+    <t>RelatedPerson.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -314,7 +317,7 @@
 </t>
   </si>
   <si>
-    <t>Person.implicitRules</t>
+    <t>RelatedPerson.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -333,7 +336,7 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>Person.language</t>
+    <t>RelatedPerson.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -361,7 +364,7 @@
     <t>Resource.language</t>
   </si>
   <si>
-    <t>Person.text</t>
+    <t>RelatedPerson.text</t>
   </si>
   <si>
     <t>narrative
@@ -391,7 +394,7 @@
     <t>Act.text?</t>
   </si>
   <si>
-    <t>Person.contained</t>
+    <t>RelatedPerson.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -421,7 +424,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Person.extension</t>
+    <t>RelatedPerson.extension</t>
   </si>
   <si>
     <t>extensions
@@ -448,7 +451,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Person.modifierExtension</t>
+    <t>RelatedPerson.modifierExtension</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -464,7 +467,7 @@
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>Person.identifier</t>
+    <t>RelatedPerson.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -477,41 +480,115 @@
     <t>Identifier for a person within a particular scope.</t>
   </si>
   <si>
-    <t>People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the person. Examples are national person identifier and local identifier.</t>
+    <t>RelatedPerson identifiers might not be unique across instances within a system, as a single human individual may be represented as many different RelatedPerson resources with different roles, periods, or relationships.</t>
+  </si>
+  <si>
+    <t>People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the patient. Examples are national person identifier and local identifier.</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>.plays:Role(classCode='IDENT').id</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>Person.active</t>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>Participant.identifier</t>
+  </si>
+  <si>
+    <t>NK1-33</t>
+  </si>
+  <si>
+    <t>RelatedPerson.active</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>This person's record is in active use</t>
-  </si>
-  <si>
-    <t>Whether this person's record is in active use.</t>
-  </si>
-  <si>
-    <t>Need to be able to mark a person record as not to be used because it was created in error.</t>
+    <t>Whether this related person's record is in active use</t>
+  </si>
+  <si>
+    <t>Whether this related person record is in active use.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>Need to be able to mark a related person record as not to be used, such as if it was created in error.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>statusCode</t>
-  </si>
-  <si>
-    <t>Person.name</t>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>Participant.active</t>
+  </si>
+  <si>
+    <t>RelatedPerson.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient)
+</t>
+  </si>
+  <si>
+    <t>The patient this person is related to</t>
+  </si>
+  <si>
+    <t>The patient this person is related to.</t>
+  </si>
+  <si>
+    <t>We need to know which patient this RelatedPerson is related to.</t>
+  </si>
+  <si>
+    <t>scoper[classCode=PSN|ANM and determinerCode='INSTANCE']/playedRole[classCode='PAT']/id</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>The relationship of the related person to the patient</t>
+  </si>
+  <si>
+    <t>The nature of the relationship between the related person and the patient.</t>
+  </si>
+  <si>
+    <t>The directionality of the relationship is from the RelatedPerson to the Patient. For example, if the Patient is a child, and the RelatedPerson is the mother, the relationship would be PRN (parent) or MTH (mother).</t>
+  </si>
+  <si>
+    <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>The nature of the relationship between a patient and the related person.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>NK1-3</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name</t>
   </si>
   <si>
     <t xml:space="preserve">HumanName
@@ -524,19 +601,19 @@
     <t>A name associated with the person.</t>
   </si>
   <si>
-    <t>Person may have multiple names with different uses or applicable periods.</t>
-  </si>
-  <si>
-    <t>Need to be able to track the person by multiple names. Examples are your official name and a partner name.</t>
-  </si>
-  <si>
-    <t>./name</t>
-  </si>
-  <si>
-    <t>PID-5, PID-9</t>
-  </si>
-  <si>
-    <t>Person.telecom</t>
+    <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Participant.name</t>
+  </si>
+  <si>
+    <t>NK1-2</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom</t>
   </si>
   <si>
     <t xml:space="preserve">ContactPoint
@@ -549,31 +626,31 @@
     <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
   </si>
   <si>
-    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently and also to help with identification.</t>
+    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
   </si>
   <si>
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>./telecom</t>
-  </si>
-  <si>
-    <t>PID-13, PID-14</t>
-  </si>
-  <si>
-    <t>Person.gender</t>
+    <t>telecom</t>
+  </si>
+  <si>
+    <t>ParticipantContactable.telecom</t>
+  </si>
+  <si>
+    <t>NK1-5 / NK1-6 / NK1-40</t>
+  </si>
+  <si>
+    <t>RelatedPerson.gender</t>
   </si>
   <si>
     <t>male | female | other | unknown</t>
   </si>
   <si>
-    <t>Administrative Gender.</t>
-  </si>
-  <si>
-    <t>The gender might not match the biological sex as determined by genetics, or the individual's preferred identification. Note that for both humans and particularly animals, there are other legitimate possibilities than M and F, though a clear majority of systems and contexts only support M and F.</t>
-  </si>
-  <si>
-    <t>Needed for identification of the person, in combination with (at least) name and birth date. Gender of person drives many clinical processes.</t>
+    <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
+  </si>
+  <si>
+    <t>Needed for identification of the person, in combination with (at least) name and birth date.</t>
   </si>
   <si>
     <t>The gender of a person used for administrative purposes.</t>
@@ -582,116 +659,60 @@
     <t>http://hl7.org/fhir/ValueSet/administrative-gender|5.0.0</t>
   </si>
   <si>
-    <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
-  </si>
-  <si>
-    <t>PID-8</t>
-  </si>
-  <si>
-    <t>Person.birthDate</t>
+    <t>administrativeGender</t>
+  </si>
+  <si>
+    <t>ParticipantLiving.gender</t>
+  </si>
+  <si>
+    <t>NK1-15</t>
+  </si>
+  <si>
+    <t>RelatedPerson.birthDate</t>
   </si>
   <si>
     <t xml:space="preserve">date
 </t>
   </si>
   <si>
-    <t>The date on which the person was born</t>
-  </si>
-  <si>
-    <t>The birth date for the person.</t>
-  </si>
-  <si>
-    <t>At least an estimated year should be provided as a guess if the real DOB is unknown.</t>
-  </si>
-  <si>
-    <t>Age of person drives many clinical processes, and is often used in performing identification of the person. Times are not included so as to not confuse things with potential timezone issues.</t>
-  </si>
-  <si>
-    <t>./birthTime</t>
-  </si>
-  <si>
-    <t>PID-7</t>
-  </si>
-  <si>
-    <t>Person.deceased[x]</t>
-  </si>
-  <si>
-    <t>boolean
-dateTime</t>
-  </si>
-  <si>
-    <t>Indicates if the individual is deceased or not</t>
-  </si>
-  <si>
-    <t>Indicates if the individual is deceased or not.</t>
-  </si>
-  <si>
-    <t>If there's no value in the instance, it means there is no statement on whether or not the individual is deceased. Most systems will interpret the absence of a value as a sign of the person being alive.</t>
-  </si>
-  <si>
-    <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedInd, player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedTime</t>
-  </si>
-  <si>
-    <t>PID-30  (bool) and PID-29 (datetime)</t>
-  </si>
-  <si>
-    <t>Person.address</t>
+    <t>The date on which the related person was born</t>
+  </si>
+  <si>
+    <t>The date on which the related person was born.</t>
+  </si>
+  <si>
+    <t>player.birthTime</t>
+  </si>
+  <si>
+    <t>ParticipantLiving.birthDate</t>
+  </si>
+  <si>
+    <t>RelatedPerson.address</t>
   </si>
   <si>
     <t xml:space="preserve">Address
 </t>
   </si>
   <si>
-    <t>One or more addresses for the person</t>
-  </si>
-  <si>
-    <t>One or more addresses for the person.</t>
-  </si>
-  <si>
-    <t>Person may have multiple addresses with different uses or applicable periods.</t>
-  </si>
-  <si>
-    <t>May need to keep track of person's addresses for contacting, billing or reporting requirements and also to help with identification.</t>
-  </si>
-  <si>
-    <t>./addr</t>
-  </si>
-  <si>
-    <t>PID-11</t>
-  </si>
-  <si>
-    <t>Person.maritalStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Marital (civil) status of a person</t>
-  </si>
-  <si>
-    <t>This field contains a person's most recent marital (civil) status.</t>
-  </si>
-  <si>
-    <t>Many countries maintain a register of births, deaths and marriages, and this would simplify that interaction</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>The domestic partnership status of a person.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
-  </si>
-  <si>
-    <t>player[classCode=PSN]/maritalStatusCode</t>
-  </si>
-  <si>
-    <t>PID-16</t>
-  </si>
-  <si>
-    <t>Person.photo</t>
+    <t>Address where the related person can be contacted or visited</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited.</t>
+  </si>
+  <si>
+    <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
+  </si>
+  <si>
+    <t>addr</t>
+  </si>
+  <si>
+    <t>ParticipantContactable.address</t>
+  </si>
+  <si>
+    <t>NK1-4</t>
+  </si>
+  <si>
+    <t>RelatedPerson.photo</t>
   </si>
   <si>
     <t xml:space="preserve">Attachment
@@ -701,39 +722,69 @@
     <t>Image of the person</t>
   </si>
   <si>
-    <t>An image that can be displayed as a thumbnail of the person to enhance the identification of the individual.</t>
-  </si>
-  <si>
-    <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/desc</t>
+    <t>Image of the person.</t>
+  </si>
+  <si>
+    <t>Many EHR systems have the capability to capture an image of persons. Fits with newer social media usage too.</t>
+  </si>
+  <si>
+    <t>player[classCode='PSN' and determinerCode='INSTANCE']/desc</t>
+  </si>
+  <si>
+    <t>ParticipantLiving.photo</t>
   </si>
   <si>
     <t>OBX-5 - needs a profile</t>
   </si>
   <si>
-    <t>Person.communication</t>
+    <t>RelatedPerson.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Period of time that this relationship is considered valid</t>
+  </si>
+  <si>
+    <t>The period of time during which this relationship is or was active. If there are no dates defined, then the interval is unknown.</t>
+  </si>
+  <si>
+    <t>If an individual has a relationship with a patient over multiple, non-adjacent periods, there should be a distinct RelatedPerson instance for each period.  For example, if a person is a roommate for a period of time, moves out, and is later a roommate with the same person again, you would have two RelatedPerson instances.</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>A language which may be used to communicate with the person about his or her health</t>
-  </si>
-  <si>
-    <t>A language which may be used to communicate with the person about his or her health.</t>
-  </si>
-  <si>
-    <t>If no language is specified, this *implies* that the default local language is spoken.  If you need to convey proficiency for multiple modes, then you need multiple Person.Communication associations.   For animals, language is not a relevant field, and should be absent from the instance. If the Patient does not speak the default local language, then the Interpreter Required Standard can be used to explicitly declare that an interpreter is required.
-Note that this property should not be used to update any linked/logically linked practitioner resources as it serves as a language that can be used to communicate with patients - however it may be used to inform the value on practitioner, along with their role at the organization (with the practitioner's permission)</t>
-  </si>
-  <si>
-    <t>If a person does not speak the local language, interpreters may be required, so languages spoken and proficiency are important things to keep track of both for person and other persons of interest.</t>
+    <t>A language which may be used to communicate with the related person about the patient's health</t>
+  </si>
+  <si>
+    <t>A language which may be used to communicate with the related person about the patient's health.</t>
+  </si>
+  <si>
+    <t>If no language is specified, this *implies* that the default local language is spoken.  If you need to convey proficiency for multiple modes, then you need multiple RelatedPerson.Communication associations.   If the RelatedPerson does not speak the default local language, then the Interpreter Required Standard can be used to explicitly declare that an interpreter is required.</t>
+  </si>
+  <si>
+    <t>If a related person does not speak the local language, interpreters may be required, so languages spoken and proficiency is an important things to keep track of both for patient and other persons of interest.</t>
   </si>
   <si>
     <t>LanguageCommunication</t>
   </si>
   <si>
-    <t>Person.communication.id</t>
+    <t>ParticipantLiving.communication</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -756,7 +807,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Person.communication.extension</t>
+    <t>RelatedPerson.communication.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -765,7 +816,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Person.communication.modifierExtension</t>
+    <t>RelatedPerson.communication.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -782,10 +833,10 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>Person.communication.language</t>
-  </si>
-  <si>
-    <t>The language which can be used to communicate with the person about his or her health</t>
+    <t>RelatedPerson.communication.language</t>
+  </si>
+  <si>
+    <t>The language which can be used to communicate with the related person about the patient's health</t>
   </si>
   <si>
     <t>The ISO-639-1 alpha 2 code in lower case for the language, optionally followed by a hyphen and the ISO-3166-1 alpha 2 code for the region in upper case; e.g. "en" for English, or "en-US" for American English versus "en-AU" for Australian English.</t>
@@ -800,16 +851,13 @@
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
   </si>
   <si>
-    <t>PID-15, LAN-2</t>
-  </si>
-  <si>
-    <t>Person.communication.preferred</t>
+    <t>RelatedPerson.communication.preferred</t>
   </si>
   <si>
     <t>Language preference indicator</t>
   </si>
   <si>
-    <t>Indicates whether or not the person prefers this language (over other languages he masters up a certain level).</t>
+    <t>Indicates whether or not the related person prefers this language (over other languages he or she masters up a certain level).</t>
   </si>
   <si>
     <t>This language is specifically identified for communicating healthcare information.</t>
@@ -819,83 +867,6 @@
   </si>
   <si>
     <t>preferenceInd</t>
-  </si>
-  <si>
-    <t>PID-15</t>
-  </si>
-  <si>
-    <t>Person.managingOrganization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>The organization that is the custodian of the person record</t>
-  </si>
-  <si>
-    <t>The organization that is the custodian of the person record.</t>
-  </si>
-  <si>
-    <t>Need to know who recognizes this person record, manages and updates it.</t>
-  </si>
-  <si>
-    <t>scoper</t>
-  </si>
-  <si>
-    <t>Person.link</t>
-  </si>
-  <si>
-    <t>Link to a resource that concerns the same actual person</t>
-  </si>
-  <si>
-    <t>Link to a resource that concerns the same actual person.</t>
-  </si>
-  <si>
-    <t>outboundLink</t>
-  </si>
-  <si>
-    <t>Person.link.id</t>
-  </si>
-  <si>
-    <t>Person.link.extension</t>
-  </si>
-  <si>
-    <t>Person.link.modifierExtension</t>
-  </si>
-  <si>
-    <t>Person.link.target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|RelatedPerson|Person)
-</t>
-  </si>
-  <si>
-    <t>The resource to which this actual person is associated</t>
-  </si>
-  <si>
-    <t>The resource to which this actual person is associated.</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>Person.link.assurance</t>
-  </si>
-  <si>
-    <t>level1 | level2 | level3 | level4</t>
-  </si>
-  <si>
-    <t>Level of assurance that this link is associated with the target resource.</t>
-  </si>
-  <si>
-    <t>The level of confidence that this link represents the same actual person, based on NIST Authentication Levels.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identity-assuranceLevel|5.0.0</t>
-  </si>
-  <si>
-    <t>priorityNumber?</t>
   </si>
 </sst>
 </file>
@@ -1197,11 +1168,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.23046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.23046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.27734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="46.27734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1210,7 +1181,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.2578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="18.296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1224,20 +1195,21 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="102.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.4140625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="67.9296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.61328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.27734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="142.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="34.56640625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="89.0078125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.15234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.37109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1358,6 +1330,9 @@
       <c r="AM1" t="s" s="1">
         <v>74</v>
       </c>
+      <c r="AN1" t="s" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
@@ -1372,10 +1347,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>19</v>
@@ -1387,17 +1362,15 @@
         <v>19</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="N2" t="s" s="2">
         <v>80</v>
       </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>19</v>
@@ -1449,10 +1422,10 @@
         <v>29</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>19</v>
@@ -1467,15 +1440,18 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1483,10 +1459,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>19</v>
@@ -1495,19 +1471,19 @@
         <v>19</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1557,13 +1533,13 @@
         <v>19</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>19</v>
@@ -1578,15 +1554,18 @@
         <v>19</v>
       </c>
       <c r="AM3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN3" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1594,10 +1573,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>19</v>
@@ -1606,16 +1585,16 @@
         <v>19</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1666,19 +1645,19 @@
         <v>19</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>19</v>
@@ -1687,15 +1666,18 @@
         <v>19</v>
       </c>
       <c r="AM4" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN4" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1703,31 +1685,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1777,19 +1759,19 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>19</v>
@@ -1798,15 +1780,18 @@
         <v>19</v>
       </c>
       <c r="AM5" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN5" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1814,10 +1799,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>19</v>
@@ -1829,16 +1814,16 @@
         <v>19</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1864,13 +1849,13 @@
         <v>19</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>19</v>
@@ -1888,19 +1873,19 @@
         <v>19</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>19</v>
@@ -1909,26 +1894,29 @@
         <v>19</v>
       </c>
       <c r="AM6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN6" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>19</v>
@@ -1940,16 +1928,16 @@
         <v>19</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1999,47 +1987,50 @@
         <v>19</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>19</v>
@@ -2051,16 +2042,16 @@
         <v>19</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2110,16 +2101,16 @@
         <v>19</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>19</v>
@@ -2128,29 +2119,32 @@
         <v>19</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>19</v>
@@ -2162,16 +2156,16 @@
         <v>19</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2221,71 +2215,74 @@
         <v>19</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>19</v>
@@ -2334,36 +2331,39 @@
         <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2371,10 +2371,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>19</v>
@@ -2383,20 +2383,22 @@
         <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>19</v>
@@ -2445,36 +2447,39 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2482,110 +2487,117 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="P12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="R12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="J12" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AI12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2593,10 +2605,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>19</v>
@@ -2605,22 +2617,20 @@
         <v>19</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>19</v>
@@ -2669,36 +2679,39 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2706,10 +2719,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>19</v>
@@ -2718,22 +2731,22 @@
         <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>19</v>
@@ -2758,13 +2771,13 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -2782,36 +2795,39 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>19</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2819,10 +2835,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>19</v>
@@ -2831,22 +2847,20 @@
         <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -2871,13 +2885,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -2895,36 +2909,39 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2932,10 +2949,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
@@ -2944,22 +2961,22 @@
         <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3008,36 +3025,39 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3045,10 +3065,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>19</v>
@@ -3057,21 +3077,21 @@
         <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
       </c>
@@ -3095,13 +3115,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -3119,36 +3139,39 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3156,10 +3179,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
@@ -3168,23 +3191,19 @@
         <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>19</v>
       </c>
@@ -3232,36 +3251,39 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3269,10 +3291,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>19</v>
@@ -3281,21 +3303,21 @@
         <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>19</v>
       </c>
@@ -3319,13 +3341,13 @@
         <v>19</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>214</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>19</v>
@@ -3343,36 +3365,39 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3380,10 +3405,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>19</v>
@@ -3395,16 +3420,18 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>19</v>
       </c>
@@ -3452,36 +3479,39 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3489,10 +3519,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>19</v>
@@ -3504,20 +3534,18 @@
         <v>19</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>19</v>
       </c>
@@ -3565,36 +3593,39 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>19</v>
+        <v>237</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3602,10 +3633,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>19</v>
@@ -3617,16 +3648,20 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>19</v>
       </c>
@@ -3674,47 +3709,50 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -3726,17 +3764,15 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>248</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>134</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -3785,72 +3821,73 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
       </c>
@@ -3898,71 +3935,74 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -3987,13 +4027,13 @@
         <v>19</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>19</v>
@@ -4011,36 +4051,39 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>19</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4048,10 +4091,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>19</v>
@@ -4063,19 +4106,19 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -4100,13 +4143,13 @@
         <v>19</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>19</v>
@@ -4124,36 +4167,39 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>258</v>
+        <v>19</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4161,10 +4207,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>19</v>
@@ -4173,20 +4219,22 @@
         <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -4235,687 +4283,30 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q28" s="2"/>
-      <c r="R28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>19</v>
       </c>
     </row>
